--- a/AAII_Financials/Quarterly/NUCL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NUCL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>NUCL</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -661,8 +661,12 @@
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -687,19 +691,19 @@
         <v>45900</v>
       </c>
       <c r="F7" s="2">
+        <v>45808</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45716</v>
+      </c>
+      <c r="H7" s="2">
         <v>45626</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45535</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>45443</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -744,11 +748,11 @@
       <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -773,11 +777,11 @@
       <c r="E10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -903,13 +907,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -942,19 +946,19 @@
         <v>1200</v>
       </c>
       <c r="F17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>800</v>
+      </c>
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+      <c r="J17" s="3">
+        <v>100</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -971,19 +975,19 @@
         <v>-1200</v>
       </c>
       <c r="F18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+      <c r="J18" s="3">
+        <v>-100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1018,14 +1022,14 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1042,19 +1046,19 @@
         <v>-1300</v>
       </c>
       <c r="F21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
@@ -1100,19 +1104,19 @@
         <v>-1300</v>
       </c>
       <c r="F23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="J23" s="3">
+        <v>-100</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1187,19 +1191,19 @@
         <v>-1300</v>
       </c>
       <c r="F26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>-100</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1216,19 +1220,19 @@
         <v>-1300</v>
       </c>
       <c r="F27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>-100</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1366,14 +1370,14 @@
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1390,19 +1394,19 @@
         <v>-1300</v>
       </c>
       <c r="F33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>-100</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1448,19 +1452,19 @@
         <v>-1300</v>
       </c>
       <c r="F35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>-100</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1482,19 +1486,19 @@
         <v>45900</v>
       </c>
       <c r="F38" s="2">
+        <v>45808</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45716</v>
+      </c>
+      <c r="H38" s="2">
         <v>45626</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45535</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="J38" s="2">
+        <v>45443</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1537,13 +1541,13 @@
         <v>3400</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
+      <c r="H41" s="3">
+        <v>0</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
@@ -1682,13 +1686,13 @@
         <v>3800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="H46" s="3">
+        <v>0</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1739,8 +1743,8 @@
       <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+      <c r="F48" s="3">
+        <v>600</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1774,14 +1778,14 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1914,13 +1918,13 @@
         <v>4600</v>
       </c>
       <c r="F54" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="H54" s="3">
+        <v>0</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -1969,13 +1973,13 @@
         <v>200</v>
       </c>
       <c r="F57" s="3">
+        <v>200</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2003,14 +2007,14 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2026,8 +2030,8 @@
       <c r="E59" s="3">
         <v>0</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2056,13 +2060,13 @@
         <v>400</v>
       </c>
       <c r="F60" s="3">
+        <v>500</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>600</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2230,13 +2234,13 @@
         <v>700</v>
       </c>
       <c r="F66" s="3">
+        <v>500</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
         <v>600</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2388,13 +2392,13 @@
         <v>-4000</v>
       </c>
       <c r="F72" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2504,13 +2508,13 @@
         <v>4000</v>
       </c>
       <c r="F76" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G76" s="3">
         <v>-600</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+      <c r="H76" s="3">
+        <v>-600</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2567,19 +2571,19 @@
         <v>45900</v>
       </c>
       <c r="F80" s="2">
+        <v>45808</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45716</v>
+      </c>
+      <c r="H80" s="2">
         <v>45626</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45535</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="J80" s="2">
+        <v>45443</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2596,19 +2600,19 @@
         <v>-1300</v>
       </c>
       <c r="F81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>-100</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2808,23 +2812,23 @@
       <c r="D89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="E89" s="3">
+        <v>-1500</v>
       </c>
       <c r="F89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2850,23 +2854,23 @@
       <c r="D91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="E91" s="3">
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -2937,23 +2941,23 @@
       <c r="D94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>-200</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3095,23 +3099,23 @@
       <c r="D100" s="3">
         <v>0</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="E100" s="3">
+        <v>300</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>3700</v>
+      </c>
+      <c r="G100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>100</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3121,8 +3125,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -3154,22 +3158,22 @@
         <v>-2100</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="F102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
